--- a/sablonlar/lexbnb-gider-sablonu.xlsx
+++ b/sablonlar/lexbnb-gider-sablonu.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Giderler" sheetId="1" r:id="rId1"/>
     <sheet name="NASIL DOLDURULUR" sheetId="2" r:id="rId2"/>
+    <sheet name="GEÇERLİ DEĞERLER" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -425,19 +426,19 @@
         <v>2026-07-03</v>
       </c>
       <c r="B2" t="str">
-        <v>Şömine &amp; Yakacak</v>
+        <v>Fatura</v>
       </c>
       <c r="C2" t="str">
         <v>18000</v>
       </c>
       <c r="D2" t="str">
-        <v>Örnek: yakacak alımı</v>
+        <v>Örnek: elektrik faturası</v>
       </c>
       <c r="E2" t="str">
         <v>OPEX</v>
       </c>
       <c r="F2" t="str">
-        <v>ALL</v>
+        <v>MULK_KODU_1</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +446,7 @@
         <v>2026-07-08</v>
       </c>
       <c r="B3" t="str">
-        <v>Bakım &amp; Onarım</v>
+        <v>Bakım</v>
       </c>
       <c r="C3" t="str">
         <v>6500</v>
@@ -465,7 +466,7 @@
         <v>2026-07-14</v>
       </c>
       <c r="B4" t="str">
-        <v>Yatırım &amp; Demirbaş</v>
+        <v>Diğer</v>
       </c>
       <c r="C4" t="str">
         <v>45000</v>
@@ -489,11 +490,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>LEXBNB — GİDER DEFTERİ ŞABLONU</v>
+        <v>LEXBNB — GİDER DEFTERİ ŞABLONU · NASIL DOLDURULUR</v>
       </c>
     </row>
     <row r="2">
@@ -503,77 +504,217 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ZORUNLU SÜTUNLAR: Tarih, Kategori, Tutar</v>
+        <v>ADIM 1 — İlk sayfadaki örnek satırları silin ya da üzerine yazın. Başlık satırı DOSYANIN İLK SATIRI olmalı.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Diğer sütunlar isteğe bağlıdır.</v>
+        <v>ADIM 2 — Her gider bir satırdır. ZORUNLU: Tarih, Kategori, Tutar.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>ADIM 3 — "Kategori": GEÇERLİ DEĞERLER sayfasındaki kategorilerden birini yazın (büyük/küçük harf önemsiz). Listede olmayan kategorinin satırı kaydedilmez ve nedeni yazılır — "Diğer"e sessizce düşmez.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1) "Villa" sütunu boş veya ALL ise gider tüm portföye yazılır.</v>
+        <v>ADIM 4 — "Villa": boş ya da ALL ise gider tüm portföye yazılır. Tek mülke yazmak için kendi mülk kodunuzu girin; MULK_KODU_1 / MULK_KODU_2 yer tutucudur, değiştirmezseniz o satır kaydedilmez.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve">   Tek bir mülke yazmak için KENDİ mülk kodunuzu girin.</v>
+        <v>ADIM 5 — "Tür": OPEX (işletme gideri) ya da CAPEX (yatırım). Boşsa OPEX.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">   MULK_KODU_1 / MULK_KODU_2 yalnızca yer tutucudur; değiştirmezseniz</v>
+        <v>ADIM 6 — Tarih: 2026-07-03 ya da 03.07.2026. Tutar: 18000 ya da 18.000,50.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">   o satırlar kaydedilmez.</v>
+        <v>ADIM 7 — Temizlik personeline ödenen tutar buraya GİRİLMEZ; temizlik görevinden gider olarak yazılır. Reklam harcamasını Kanallar ve Pazarlama ekranından girin; burada da girilirse iki kez sayılır.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2) "Tür": OPEX (işletme gideri) veya CAPEX (yatırım). Boşsa OPEX sayılır.</v>
+        <v>ADIM 8 — Kaydedip Araçlar › Excel / CSV yükle ekranına bırakın. Önizlemede hatalı satırları ve nedenini görürsünüz; onaylamadan hiçbir şey kaydedilmez.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B23"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>KATEGORİLER — "Kategori" sütununa KATEGORİ adını yazın</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Kategori</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Neleri kapsar</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Maaş</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Maaş (Personel / Yönetici)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Temizlik</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Temizlik &amp; Çamaşırhane</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Bakım</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Bakım, Onarım &amp; Tesisat</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Reklam</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Reklam &amp; Pazarlama (Meta/Google)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Akaryakıt</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Akaryakıt &amp; Ulaşım</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Fatura</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Fatura (Elektrik, Su, İnternet)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Muhasebe</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Muhasebe &amp; Hukuk</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Kredi Kartı / Komisyon</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Kredi Kartı / Komisyon</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>3) Tarih: 2026-07-03 veya 03.07.2026 — ikisi de kabul edilir.</v>
+        <v>Danışmanlık</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Danışmanlık &amp; Yazılım</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>4) Tutar: 18000 veya 18.000,50 — ikisi de kabul edilir.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5) Başlık satırı DOSYANIN İLK SATIRI olmalıdır.</v>
+        <v>Diğer</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Diğer Giderler</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>MÜLKLER — "Villa" sütunu (boş ya da ALL = tüm portföy)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>NOT: Temizlik personeline ödenen tutar buraya GİRİLMEZ; o, rezervasyonun</v>
+        <v>Kod</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Ad</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>temizlik görevinden otomatik gider yazılır.</v>
+        <v>ALL</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Tüm portföy</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>MULK_KODU_1</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Araçlar › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>MULK_KODU_2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Araçlar › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TÜR — "Tür" sütunu</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Değer</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Anlamı</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="B22" t="str">
+        <v>İşletme gideri (boşsa bu sayılır)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CAPEX</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Yatırım / demirbaş</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sablonlar/lexbnb-gider-sablonu.xlsx
+++ b/sablonlar/lexbnb-gider-sablonu.xlsx
@@ -534,7 +534,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ADIM 7 — Temizlik personeline ödenen tutar buraya GİRİLMEZ; temizlik görevinden gider olarak yazılır. Reklam harcamasını Kanallar ve Pazarlama ekranından girin; burada da girilirse iki kez sayılır.</v>
+        <v>ADIM 7 — Temizlik personeline ödenen tutar buraya GİRİLMEZ: yeni temizlikler görevden gider yazılır, GEÇMİŞ temizlikler için Geçmiş Temizlik şablonunu kullanın. Reklam harcamasını Kanallar ve Pazarlama ekranından girin; burada da girilirse iki kez sayılır.</v>
       </c>
     </row>
     <row r="10">

--- a/sablonlar/lexbnb-gider-sablonu.xlsx
+++ b/sablonlar/lexbnb-gider-sablonu.xlsx
@@ -539,7 +539,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ADIM 8 — Kaydedip Araçlar › Excel / CSV yükle ekranına bırakın. Önizlemede hatalı satırları ve nedenini görürsünüz; onaylamadan hiçbir şey kaydedilmez.</v>
+        <v>ADIM 8 — Kaydedip Veri ve yardım › Excel / CSV yükle ekranına bırakın. Önizlemede hatalı satırları ve nedenini görürsünüz; onaylamadan hiçbir şey kaydedilmez.</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -640,81 +640,97 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Diğer</v>
+        <v>Demirbaş</v>
       </c>
       <c r="B12" t="str">
-        <v>Diğer Giderler</v>
+        <v>Demirbaş &amp; Ekipman (klima, beyaz eşya, mobilya)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Tadilat</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Tadilat &amp; Yenileme</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>MÜLKLER — "Villa" sütunu (boş ya da ALL = tüm portföy)</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Kod</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Ad</v>
+        <v>Diğer</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Diğer Giderler</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ALL</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Tüm portföy</v>
+        <v>MÜLKLER — "Villa" sütunu (boş ya da ALL = tüm portföy)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>MULK_KODU_1</v>
+        <v>Kod</v>
       </c>
       <c r="B17" t="str">
-        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Araçlar › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
+        <v>Ad</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>MULK_KODU_2</v>
+        <v>ALL</v>
       </c>
       <c r="B18" t="str">
-        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Araçlar › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
+        <v>Tüm portföy</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>MULK_KODU_1</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Veri ve yardım › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TÜR — "Tür" sütunu</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Değer</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Anlamı</v>
+        <v>MULK_KODU_2</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Veri ve yardım › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>OPEX</v>
-      </c>
-      <c r="B22" t="str">
-        <v>İşletme gideri (boşsa bu sayılır)</v>
+        <v>TÜR — "Tür" sütunu</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
+        <v>Değer</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Anlamı</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="B24" t="str">
+        <v>İşletme gideri (boşsa bu sayılır)</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
         <v>CAPEX</v>
       </c>
-      <c r="B23" t="str">
+      <c r="B25" t="str">
         <v>Yatırım / demirbaş</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B25"/>
   </ignoredErrors>
 </worksheet>
 </file>